--- a/Du_Lieu_Mau_He_Thong/Bieu_mau_dang_ky_dich_vu_ngan_hang_so_VCB_Digibank_va_Smart_OTP_2026.xlsx
+++ b/Du_Lieu_Mau_He_Thong/Bieu_mau_dang_ky_dich_vu_ngan_hang_so_VCB_Digibank_va_Smart_OTP_2026.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DataSheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -33,10 +33,10 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <sz val="10"/>
+      <sz val="10.5"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -47,6 +47,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="0000843D"/>
         <bgColor rgb="0000843D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4F9F5"/>
+        <bgColor rgb="00F4F9F5"/>
       </patternFill>
     </fill>
   </fills>
@@ -76,13 +82,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -452,14 +467,14 @@
   <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Gói dịch vụ Ngân hàng số</t>
@@ -477,30 +492,26 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Phương thức xác thực</t>
+          <t>Phương thức xác thực an toàn</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Phí duy trì</t>
+          <t>Phí duy trì dịch vụ</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Gói Cơ bản (Khởi đầu)</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>100,000,000</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>500,000,000</t>
-        </is>
+      <c r="B2" s="3" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>500000000</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -509,52 +520,44 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Miễn phí</t>
+          <t>Miễn phí trọn đời</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Gói Nâng cao (Tiêu chuẩn)</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>1,000,000,000</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>3,000,000,000</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="B3" s="5" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>3000000000</v>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>VCB Smart OTP tích hợp App</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Miễn phí</t>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Miễn phí trọn đời</t>
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="24" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Gói Priority VIP</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>3,000,000,000</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>10,000,000,000</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>3000000000</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>10000000000</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -563,34 +566,30 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Miễn phí</t>
+          <t>Miễn phí trọn đời</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Gói Doanh nghiệp &amp; Chủ hộ KD</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>5,000,000,000</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>20,000,000,000</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="B5" s="5" t="n">
+        <v>5000000000</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>20000000000</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Hard Token OTP / Chữ ký số CA</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Miễn phí</t>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Miễn phí trọn đời</t>
         </is>
       </c>
     </row>
